--- a/data/trans_camb/LAWTONB_2R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 9,02</t>
+          <t>-8,58; 10,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 9,57</t>
+          <t>-8,73; 9,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 15,96</t>
+          <t>-0,34; 16,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 18,92</t>
+          <t>1,22; 18,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 17,53</t>
+          <t>-2,17; 16,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 25,48</t>
+          <t>10,39; 25,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 12,14</t>
+          <t>-1,0; 12,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 10,49</t>
+          <t>-2,88; 10,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 19,25</t>
+          <t>7,39; 18,81</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 73,02</t>
+          <t>-39,65; 83,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 77,14</t>
+          <t>-38,72; 78,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 132,22</t>
+          <t>-0,84; 143,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 155,17</t>
+          <t>3,0; 155,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 148,06</t>
+          <t>-14,63; 119,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,6; 219,1</t>
+          <t>45,17; 208,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 85,64</t>
+          <t>-5,12; 87,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 70,58</t>
+          <t>-14,56; 75,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,86; 148,13</t>
+          <t>34,88; 142,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 20,09</t>
+          <t>1,57; 19,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 10,7</t>
+          <t>-5,17; 9,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 11,3</t>
+          <t>-2,33; 11,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 19,43</t>
+          <t>0,6; 20,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 13,62</t>
+          <t>-4,58; 14,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 16,22</t>
+          <t>1,58; 16,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 18,25</t>
+          <t>4,14; 17,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 9,49</t>
+          <t>-2,46; 10,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,07</t>
+          <t>1,72; 12,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 201,03</t>
+          <t>4,3; 201,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,91; 102,96</t>
+          <t>-30,45; 104,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 114,21</t>
+          <t>-14,77; 135,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 123,0</t>
+          <t>0,55; 127,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 87,34</t>
+          <t>-18,94; 94,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 106,4</t>
+          <t>6,31; 106,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 126,86</t>
+          <t>18,5; 120,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 66,16</t>
+          <t>-11,74; 66,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 84,08</t>
+          <t>7,69; 89,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 21,79</t>
+          <t>0,05; 21,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 9,64</t>
+          <t>-7,84; 9,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 4,64</t>
+          <t>-10,42; 4,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 25,73</t>
+          <t>6,2; 26,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 25,32</t>
+          <t>5,0; 25,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 13,2</t>
+          <t>-18,19; 13,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,17</t>
+          <t>6,21; 21,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 16,12</t>
+          <t>1,85; 16,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 6,57</t>
+          <t>-12,33; 7,41</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 350,73</t>
+          <t>-3,79; 326,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 146,77</t>
+          <t>-50,44; 145,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 79,46</t>
+          <t>-62,3; 72,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33,4; 266,3</t>
+          <t>29,25; 265,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,76; 252,83</t>
+          <t>24,49; 274,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,26; 105,82</t>
+          <t>-84,78; 113,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,65; 225,15</t>
+          <t>35,72; 219,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,23; 166,27</t>
+          <t>9,65; 170,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 56,7</t>
+          <t>-70,83; 64,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 18,6</t>
+          <t>2,19; 18,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 10,29</t>
+          <t>-2,66; 10,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,45</t>
+          <t>-2,37; 10,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 5,75</t>
+          <t>-9,33; 5,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 6,54</t>
+          <t>-9,74; 6,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,09</t>
+          <t>-3,65; 10,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 8,74</t>
+          <t>-2,42; 8,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 5,68</t>
+          <t>-5,29; 6,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,0</t>
+          <t>-1,19; 8,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,54; 271,13</t>
+          <t>11,48; 285,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 157,16</t>
+          <t>-23,75; 174,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 158,68</t>
+          <t>-17,6; 167,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 34,74</t>
+          <t>-36,9; 36,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 38,84</t>
+          <t>-38,23; 38,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 61,82</t>
+          <t>-14,79; 60,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 60,98</t>
+          <t>-13,27; 63,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 42,77</t>
+          <t>-27,06; 47,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 59,39</t>
+          <t>-6,05; 61,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 12,95</t>
+          <t>3,45; 12,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,0</t>
+          <t>-1,86; 6,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,1</t>
+          <t>0,04; 7,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,11</t>
+          <t>3,29; 12,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,18</t>
+          <t>0,18; 9,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 11,13</t>
+          <t>-6,6; 11,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,88</t>
+          <t>4,51; 11,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,9</t>
+          <t>0,73; 7,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 8,02</t>
+          <t>-3,15; 7,88</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>20,96; 117,76</t>
+          <t>22,5; 117,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 56,32</t>
+          <t>-12,48; 60,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 65,22</t>
+          <t>-0,84; 67,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,02; 73,01</t>
+          <t>15,41; 74,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,49; 55,22</t>
+          <t>0,65; 59,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 63,4</t>
+          <t>-34,78; 62,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,17; 72,97</t>
+          <t>25,45; 76,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,21; 46,54</t>
+          <t>3,94; 46,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 52,2</t>
+          <t>-16,75; 51,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,97</t>
+          <t>17,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,49</t>
+          <t>13,01</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 10,12</t>
+          <t>-8,16; 10,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 9,54</t>
+          <t>-8,86; 9,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 16,83</t>
+          <t>-1,79; 15,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 18,99</t>
+          <t>0,92; 19,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 16,32</t>
+          <t>-3,01; 15,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 25,02</t>
+          <t>9,64; 25,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 12,03</t>
+          <t>-1,66; 12,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 10,47</t>
+          <t>-2,76; 10,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 18,81</t>
+          <t>7,31; 18,91</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>104,91%</t>
+          <t>104,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 83,64</t>
+          <t>-38,67; 88,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 78,55</t>
+          <t>-41,88; 78,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 143,01</t>
+          <t>-7,44; 140,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 155,23</t>
+          <t>3,17; 157,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 119,07</t>
+          <t>-14,64; 119,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,17; 208,58</t>
+          <t>40,13; 207,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 87,66</t>
+          <t>-8,75; 84,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 75,24</t>
+          <t>-14,42; 77,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,88; 142,15</t>
+          <t>34,5; 137,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>8,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>6,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 19,95</t>
+          <t>1,54; 19,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 9,98</t>
+          <t>-4,7; 10,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 11,76</t>
+          <t>-3,26; 11,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 20,78</t>
+          <t>1,83; 19,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 14,33</t>
+          <t>-4,84; 13,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 16,24</t>
+          <t>0,39; 15,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 17,44</t>
+          <t>3,98; 16,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 10,1</t>
+          <t>-2,79; 10,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,42</t>
+          <t>1,28; 11,9</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 201,55</t>
+          <t>7,78; 201,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 104,95</t>
+          <t>-25,15; 116,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 135,57</t>
+          <t>-17,88; 120,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 127,84</t>
+          <t>4,13; 123,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 94,68</t>
+          <t>-19,84; 83,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 106,44</t>
+          <t>-0,4; 100,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,5; 120,6</t>
+          <t>19,45; 116,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 66,49</t>
+          <t>-12,71; 72,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,69; 89,06</t>
+          <t>6,36; 83,77</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-2,34</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,16</t>
+          <t>4,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 21,99</t>
+          <t>0,28; 22,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 9,17</t>
+          <t>-8,58; 10,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 4,58</t>
+          <t>-10,99; 4,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 26,48</t>
+          <t>4,88; 25,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 25,28</t>
+          <t>3,58; 24,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 13,96</t>
+          <t>2,82; 18,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 21,08</t>
+          <t>6,17; 20,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 16,09</t>
+          <t>1,81; 15,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 7,41</t>
+          <t>-1,12; 10,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-16,4%</t>
+          <t>-21,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-21,21%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,03%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 326,25</t>
+          <t>-2,94; 369,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 145,64</t>
+          <t>-53,81; 160,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 72,51</t>
+          <t>-63,77; 75,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,25; 265,86</t>
+          <t>22,8; 251,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,49; 274,66</t>
+          <t>17,17; 246,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 113,51</t>
+          <t>11,69; 199,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,72; 219,07</t>
+          <t>38,31; 221,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 170,62</t>
+          <t>7,56; 165,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 64,42</t>
+          <t>-8,37; 112,58</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,4</t>
+          <t>2,43; 19,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 10,77</t>
+          <t>-3,38; 9,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,15</t>
+          <t>-2,23; 8,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 5,79</t>
+          <t>-9,42; 6,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 6,69</t>
+          <t>-9,63; 5,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 10,23</t>
+          <t>-2,72; 11,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,8</t>
+          <t>-2,97; 8,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,16</t>
+          <t>-5,18; 5,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,35</t>
+          <t>-1,34; 8,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,48; 285,35</t>
+          <t>14,24; 270,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 174,2</t>
+          <t>-26,89; 150,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 167,37</t>
+          <t>-17,95; 142,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 36,42</t>
+          <t>-37,05; 39,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 38,82</t>
+          <t>-39,91; 35,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 60,57</t>
+          <t>-10,55; 72,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 63,73</t>
+          <t>-15,68; 60,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 47,95</t>
+          <t>-27,98; 40,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 61,92</t>
+          <t>-6,89; 67,94</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>6,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,68</t>
+          <t>3,25; 12,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,21</t>
+          <t>-1,55; 6,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,14</t>
+          <t>-0,65; 6,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,2</t>
+          <t>3,03; 12,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,47</t>
+          <t>0,17; 9,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 11,08</t>
+          <t>6,31; 13,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,03</t>
+          <t>4,38; 10,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,65; 6,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 7,88</t>
+          <t>4,03; 9,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>22,5; 117,73</t>
+          <t>20,35; 112,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 60,9</t>
+          <t>-10,7; 60,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 67,21</t>
+          <t>-3,98; 65,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,41; 74,93</t>
+          <t>14,16; 75,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,65; 59,64</t>
+          <t>0,17; 56,97</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 62,42</t>
+          <t>30,66; 87,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,45; 76,46</t>
+          <t>24,38; 72,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,94; 46,12</t>
+          <t>3,36; 45,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 51,68</t>
+          <t>22,35; 69,0</t>
         </is>
       </c>
     </row>
